--- a/uploads/costs/Cout_2.xlsx
+++ b/uploads/costs/Cout_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hthompson\OneDrive - PATH\Documents\github\malaria-budgeting-tool\uploads\costs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99E8DB9-7501-4A80-96D9-79D0831E2625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EACD37-3C71-4CDA-84E4-6484508573E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E72D83C0-31FE-469B-BB4E-361133B71EB0}"/>
   </bookViews>
